--- a/statsdata.xlsx
+++ b/statsdata.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sadiemagennis/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sadiemagennis/Downloads/Project_Stats/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6FEB8548-7F1F-244F-BCAB-9F7AD5822C84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{570C92AB-E59F-584A-AABF-7DED5070CD84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="480" yWindow="760" windowWidth="18080" windowHeight="9900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
